--- a/results/stress/P3_isru_zbo_adapted_MANDATORY_STRESS/results.xlsx
+++ b/results/stress/P3_isru_zbo_adapted_MANDATORY_STRESS/results.xlsx
@@ -1559,19 +1559,19 @@
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>4.944420000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.045</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>12.32876712328767</v>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1669,7 +1669,7 @@
         <v>153.0518</v>
       </c>
       <c r="P3" t="n">
-        <v>6.887331000000001</v>
+        <v>6.887331</v>
       </c>
       <c r="Q3" t="n">
         <v>0.04500000000000001</v>
@@ -1749,7 +1749,7 @@
         <v>207.9471</v>
       </c>
       <c r="P4" t="n">
-        <v>5.926492350000001</v>
+        <v>5.92649235</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0285</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.131628207280301e-14</v>
+        <v>3.552713678800501e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1802,19 +1802,19 @@
         <v>287.5</v>
       </c>
       <c r="G5" t="n">
-        <v>195.4999999999999</v>
+        <v>195.5</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>35.44551565000008</v>
@@ -1823,13 +1823,13 @@
         <v>45.37026925000009</v>
       </c>
       <c r="N5" t="n">
-        <v>346.0372000000001</v>
+        <v>346.0372</v>
       </c>
       <c r="O5" t="n">
-        <v>301.0372000000001</v>
+        <v>301.0372</v>
       </c>
       <c r="P5" t="n">
-        <v>3.612446400000001</v>
+        <v>3.6124464</v>
       </c>
       <c r="Q5" t="n">
         <v>0.012</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>-5.684341886080801e-14</v>
       </c>
     </row>
     <row r="6">
@@ -1879,28 +1879,28 @@
         <v>241.5</v>
       </c>
       <c r="F6" t="n">
-        <v>368.0000000000001</v>
+        <v>368</v>
       </c>
       <c r="G6" t="n">
-        <v>241.5</v>
+        <v>241.4999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="L6" t="n">
         <v>45.37026925000009</v>
       </c>
       <c r="M6" t="n">
-        <v>55.29499045000006</v>
+        <v>55.29499044999989</v>
       </c>
       <c r="N6" t="n">
         <v>412.5149</v>
@@ -1921,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>50.33262985000007</v>
+        <v>50.33262984999999</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>2.273736754432321e-13</v>
       </c>
     </row>
     <row r="7">
@@ -1965,22 +1965,22 @@
         <v>287.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>55.29499045000006</v>
+        <v>55.29499044999989</v>
       </c>
       <c r="M7" t="n">
-        <v>21.75499045000019</v>
+        <v>21.75499045000002</v>
       </c>
       <c r="N7" t="n">
         <v>420</v>
@@ -2001,7 +2001,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>38.52499045000013</v>
+        <v>38.52499044999995</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-9.237055564881302e-14</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
   </sheetData>
@@ -4875,7 +4875,7 @@
         <v>26.0031</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3120372000000001</v>
+        <v>0.3120372</v>
       </c>
       <c r="L40" t="n">
         <v>53.73403738333341</v>
@@ -4946,7 +4946,7 @@
         <v>26.0031</v>
       </c>
       <c r="K41" t="n">
-        <v>0.3120372000000001</v>
+        <v>0.3120372</v>
       </c>
       <c r="L41" t="n">
         <v>55.46676685000008</v>
@@ -5017,7 +5017,7 @@
         <v>26.0031</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3120372000000001</v>
+        <v>0.3120372</v>
       </c>
       <c r="L42" t="n">
         <v>57.19949631666675</v>
@@ -5088,7 +5088,7 @@
         <v>26.0031</v>
       </c>
       <c r="K43" t="n">
-        <v>0.3120372000000001</v>
+        <v>0.3120372</v>
       </c>
       <c r="L43" t="n">
         <v>58.93222578333341</v>
@@ -5159,7 +5159,7 @@
         <v>26.0031</v>
       </c>
       <c r="K44" t="n">
-        <v>0.3120372000000001</v>
+        <v>0.3120372</v>
       </c>
       <c r="L44" t="n">
         <v>60.66495525000008</v>
@@ -5230,7 +5230,7 @@
         <v>26.0031</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3120372000000001</v>
+        <v>0.3120372</v>
       </c>
       <c r="L45" t="n">
         <v>62.39768471666675</v>
@@ -5301,7 +5301,7 @@
         <v>26.0031</v>
       </c>
       <c r="K46" t="n">
-        <v>0.3120372000000001</v>
+        <v>0.3120372</v>
       </c>
       <c r="L46" t="n">
         <v>64.13041418333341</v>
@@ -5372,7 +5372,7 @@
         <v>26.0031</v>
       </c>
       <c r="K47" t="n">
-        <v>0.3120372000000001</v>
+        <v>0.3120372</v>
       </c>
       <c r="L47" t="n">
         <v>65.86314365000008</v>
@@ -5443,7 +5443,7 @@
         <v>26.0031</v>
       </c>
       <c r="K48" t="n">
-        <v>0.3120372000000001</v>
+        <v>0.3120372</v>
       </c>
       <c r="L48" t="n">
         <v>67.59587311666675</v>
@@ -5514,7 +5514,7 @@
         <v>26.0031</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3120372000000001</v>
+        <v>0.3120372</v>
       </c>
       <c r="L49" t="n">
         <v>69.32860258333342</v>
@@ -5588,7 +5588,7 @@
         <v>0.3825149</v>
       </c>
       <c r="L50" t="n">
-        <v>76.86399601666676</v>
+        <v>76.86399601666675</v>
       </c>
       <c r="M50" t="n">
         <v>30.66666666666667</v>
@@ -5609,7 +5609,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>46.19732935000009</v>
+        <v>46.19732935000008</v>
       </c>
       <c r="T50" t="n">
         <v>2.747027958000005</v>
@@ -5647,7 +5647,7 @@
         <v>0.012</v>
       </c>
       <c r="H51" t="n">
-        <v>46.19732935000009</v>
+        <v>46.19732935000008</v>
       </c>
       <c r="I51" t="n">
         <v>34.37624166666667</v>
@@ -5659,7 +5659,7 @@
         <v>0.3825149</v>
       </c>
       <c r="L51" t="n">
-        <v>77.69105611666676</v>
+        <v>77.69105611666673</v>
       </c>
       <c r="M51" t="n">
         <v>30.66666666666667</v>
@@ -5680,10 +5680,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>47.02438945000009</v>
+        <v>47.02438945000006</v>
       </c>
       <c r="T51" t="n">
-        <v>2.796651564000005</v>
+        <v>2.796651564000004</v>
       </c>
       <c r="U51" t="n">
         <v>15.83333333333333</v>
@@ -5718,7 +5718,7 @@
         <v>0.012</v>
       </c>
       <c r="H52" t="n">
-        <v>47.02438945000009</v>
+        <v>47.02438945000006</v>
       </c>
       <c r="I52" t="n">
         <v>34.37624166666667</v>
@@ -5730,7 +5730,7 @@
         <v>0.3825149</v>
       </c>
       <c r="L52" t="n">
-        <v>78.51811621666675</v>
+        <v>78.51811621666671</v>
       </c>
       <c r="M52" t="n">
         <v>30.66666666666667</v>
@@ -5751,10 +5751,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>47.85144955000008</v>
+        <v>47.85144955000004</v>
       </c>
       <c r="T52" t="n">
-        <v>2.846275170000005</v>
+        <v>2.846275170000003</v>
       </c>
       <c r="U52" t="n">
         <v>15.83333333333333</v>
@@ -5789,7 +5789,7 @@
         <v>0.012</v>
       </c>
       <c r="H53" t="n">
-        <v>47.85144955000008</v>
+        <v>47.85144955000004</v>
       </c>
       <c r="I53" t="n">
         <v>34.37624166666667</v>
@@ -5801,7 +5801,7 @@
         <v>0.3825149</v>
       </c>
       <c r="L53" t="n">
-        <v>79.34517631666675</v>
+        <v>79.3451763166667</v>
       </c>
       <c r="M53" t="n">
         <v>30.66666666666667</v>
@@ -5822,10 +5822,10 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>48.67850965000008</v>
+        <v>48.67850965000002</v>
       </c>
       <c r="T53" t="n">
-        <v>2.895898776000005</v>
+        <v>2.895898776000001</v>
       </c>
       <c r="U53" t="n">
         <v>15.83333333333333</v>
@@ -5860,7 +5860,7 @@
         <v>0.012</v>
       </c>
       <c r="H54" t="n">
-        <v>48.67850965000008</v>
+        <v>48.67850965000002</v>
       </c>
       <c r="I54" t="n">
         <v>34.37624166666667</v>
@@ -5872,7 +5872,7 @@
         <v>0.3825149</v>
       </c>
       <c r="L54" t="n">
-        <v>80.17223641666675</v>
+        <v>80.17223641666668</v>
       </c>
       <c r="M54" t="n">
         <v>30.66666666666667</v>
@@ -5893,10 +5893,10 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>49.50556975000008</v>
+        <v>49.50556975000001</v>
       </c>
       <c r="T54" t="n">
-        <v>2.945522382000005</v>
+        <v>2.945522382</v>
       </c>
       <c r="U54" t="n">
         <v>15.83333333333333</v>
@@ -5931,7 +5931,7 @@
         <v>0.012</v>
       </c>
       <c r="H55" t="n">
-        <v>49.50556975000008</v>
+        <v>49.50556975000001</v>
       </c>
       <c r="I55" t="n">
         <v>34.37624166666667</v>
@@ -5943,7 +5943,7 @@
         <v>0.3825149</v>
       </c>
       <c r="L55" t="n">
-        <v>80.99929651666675</v>
+        <v>80.99929651666666</v>
       </c>
       <c r="M55" t="n">
         <v>30.66666666666667</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>50.33262985000007</v>
+        <v>50.33262984999999</v>
       </c>
       <c r="T55" t="n">
-        <v>2.995145988000004</v>
+        <v>2.995145988</v>
       </c>
       <c r="U55" t="n">
         <v>15.83333333333333</v>
@@ -6002,7 +6002,7 @@
         <v>0.012</v>
       </c>
       <c r="H56" t="n">
-        <v>50.33262985000007</v>
+        <v>50.33262984999999</v>
       </c>
       <c r="I56" t="n">
         <v>34.37624166666667</v>
@@ -6014,7 +6014,7 @@
         <v>0.3825149</v>
       </c>
       <c r="L56" t="n">
-        <v>81.82635661666674</v>
+        <v>81.82635661666664</v>
       </c>
       <c r="M56" t="n">
         <v>30.66666666666667</v>
@@ -6035,10 +6035,10 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>51.15968995000007</v>
+        <v>51.15968994999997</v>
       </c>
       <c r="T56" t="n">
-        <v>3.044769594000004</v>
+        <v>3.044769593999999</v>
       </c>
       <c r="U56" t="n">
         <v>15.83333333333333</v>
@@ -6073,7 +6073,7 @@
         <v>0.012</v>
       </c>
       <c r="H57" t="n">
-        <v>51.15968995000007</v>
+        <v>51.15968994999997</v>
       </c>
       <c r="I57" t="n">
         <v>34.37624166666667</v>
@@ -6085,7 +6085,7 @@
         <v>0.3825149</v>
       </c>
       <c r="L57" t="n">
-        <v>82.65341671666674</v>
+        <v>82.65341671666663</v>
       </c>
       <c r="M57" t="n">
         <v>30.66666666666667</v>
@@ -6106,10 +6106,10 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>51.98675005000007</v>
+        <v>51.98675004999996</v>
       </c>
       <c r="T57" t="n">
-        <v>3.094393200000004</v>
+        <v>3.094393199999998</v>
       </c>
       <c r="U57" t="n">
         <v>15.83333333333333</v>
@@ -6144,7 +6144,7 @@
         <v>0.012</v>
       </c>
       <c r="H58" t="n">
-        <v>51.98675005000007</v>
+        <v>51.98675004999996</v>
       </c>
       <c r="I58" t="n">
         <v>34.37624166666667</v>
@@ -6156,7 +6156,7 @@
         <v>0.3825149</v>
       </c>
       <c r="L58" t="n">
-        <v>83.48047681666674</v>
+        <v>83.48047681666661</v>
       </c>
       <c r="M58" t="n">
         <v>30.66666666666667</v>
@@ -6177,10 +6177,10 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>52.81381015000007</v>
+        <v>52.81381014999994</v>
       </c>
       <c r="T58" t="n">
-        <v>3.144016806000004</v>
+        <v>3.144016805999997</v>
       </c>
       <c r="U58" t="n">
         <v>15.83333333333333</v>
@@ -6215,7 +6215,7 @@
         <v>0.012</v>
       </c>
       <c r="H59" t="n">
-        <v>52.81381015000007</v>
+        <v>52.81381014999994</v>
       </c>
       <c r="I59" t="n">
         <v>34.37624166666667</v>
@@ -6227,7 +6227,7 @@
         <v>0.3825149</v>
       </c>
       <c r="L59" t="n">
-        <v>84.30753691666673</v>
+        <v>84.30753691666659</v>
       </c>
       <c r="M59" t="n">
         <v>30.66666666666667</v>
@@ -6248,10 +6248,10 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>53.64087025000006</v>
+        <v>53.64087024999992</v>
       </c>
       <c r="T59" t="n">
-        <v>3.193640412000004</v>
+        <v>3.193640411999996</v>
       </c>
       <c r="U59" t="n">
         <v>15.83333333333333</v>
@@ -6286,7 +6286,7 @@
         <v>0.012</v>
       </c>
       <c r="H60" t="n">
-        <v>53.64087025000006</v>
+        <v>53.64087024999992</v>
       </c>
       <c r="I60" t="n">
         <v>34.37624166666667</v>
@@ -6298,7 +6298,7 @@
         <v>0.3825149</v>
       </c>
       <c r="L60" t="n">
-        <v>85.13459701666673</v>
+        <v>85.13459701666658</v>
       </c>
       <c r="M60" t="n">
         <v>30.66666666666667</v>
@@ -6319,10 +6319,10 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>54.46793035000006</v>
+        <v>54.4679303499999</v>
       </c>
       <c r="T60" t="n">
-        <v>3.243264018000004</v>
+        <v>3.243264017999995</v>
       </c>
       <c r="U60" t="n">
         <v>15.83333333333333</v>
@@ -6357,7 +6357,7 @@
         <v>0.012</v>
       </c>
       <c r="H61" t="n">
-        <v>54.46793035000006</v>
+        <v>54.4679303499999</v>
       </c>
       <c r="I61" t="n">
         <v>34.37624166666667</v>
@@ -6369,7 +6369,7 @@
         <v>0.3825149</v>
       </c>
       <c r="L61" t="n">
-        <v>85.96165711666673</v>
+        <v>85.96165711666656</v>
       </c>
       <c r="M61" t="n">
         <v>30.66666666666667</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>55.29499045000006</v>
+        <v>55.29499044999989</v>
       </c>
       <c r="T61" t="n">
-        <v>3.292887624000004</v>
+        <v>3.292887623999993</v>
       </c>
       <c r="U61" t="n">
         <v>15.83333333333333</v>
@@ -6428,7 +6428,7 @@
         <v>0.012</v>
       </c>
       <c r="H62" t="n">
-        <v>55.29499045000006</v>
+        <v>55.29499044999989</v>
       </c>
       <c r="I62" t="n">
         <v>35</v>
@@ -6440,7 +6440,7 @@
         <v>0.42</v>
       </c>
       <c r="L62" t="n">
-        <v>89.87499045000006</v>
+        <v>89.87499044999988</v>
       </c>
       <c r="M62" t="n">
         <v>37.37499999999999</v>
@@ -6461,10 +6461,10 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>52.49999045000006</v>
+        <v>52.49999044999989</v>
       </c>
       <c r="T62" t="n">
-        <v>3.233849427000004</v>
+        <v>3.233849426999993</v>
       </c>
       <c r="U62" t="n">
         <v>15.83333333333333</v>
@@ -6499,7 +6499,7 @@
         <v>0.012</v>
       </c>
       <c r="H63" t="n">
-        <v>52.49999045000006</v>
+        <v>52.49999044999989</v>
       </c>
       <c r="I63" t="n">
         <v>35</v>
@@ -6511,7 +6511,7 @@
         <v>0.42</v>
       </c>
       <c r="L63" t="n">
-        <v>87.07999045000007</v>
+        <v>87.0799904499999</v>
       </c>
       <c r="M63" t="n">
         <v>37.37499999999999</v>
@@ -6532,10 +6532,10 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>49.70499045000007</v>
+        <v>49.7049904499999</v>
       </c>
       <c r="T63" t="n">
-        <v>3.066149427000004</v>
+        <v>3.066149426999994</v>
       </c>
       <c r="U63" t="n">
         <v>15.83333333333333</v>
@@ -6570,7 +6570,7 @@
         <v>0.012</v>
       </c>
       <c r="H64" t="n">
-        <v>49.70499045000007</v>
+        <v>49.7049904499999</v>
       </c>
       <c r="I64" t="n">
         <v>35</v>
@@ -6582,7 +6582,7 @@
         <v>0.42</v>
       </c>
       <c r="L64" t="n">
-        <v>84.28499045000008</v>
+        <v>84.28499044999991</v>
       </c>
       <c r="M64" t="n">
         <v>37.37499999999999</v>
@@ -6603,10 +6603,10 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>46.90999045000009</v>
+        <v>46.90999044999992</v>
       </c>
       <c r="T64" t="n">
-        <v>2.898449427000005</v>
+        <v>2.898449426999994</v>
       </c>
       <c r="U64" t="n">
         <v>15.83333333333333</v>
@@ -6641,7 +6641,7 @@
         <v>0.012</v>
       </c>
       <c r="H65" t="n">
-        <v>46.90999045000009</v>
+        <v>46.90999044999992</v>
       </c>
       <c r="I65" t="n">
         <v>35</v>
@@ -6653,7 +6653,7 @@
         <v>0.42</v>
       </c>
       <c r="L65" t="n">
-        <v>81.48999045000009</v>
+        <v>81.48999044999992</v>
       </c>
       <c r="M65" t="n">
         <v>37.37499999999999</v>
@@ -6674,10 +6674,10 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>44.1149904500001</v>
+        <v>44.11499044999993</v>
       </c>
       <c r="T65" t="n">
-        <v>2.730749427000006</v>
+        <v>2.730749426999995</v>
       </c>
       <c r="U65" t="n">
         <v>15.83333333333333</v>
@@ -6712,7 +6712,7 @@
         <v>0.012</v>
       </c>
       <c r="H66" t="n">
-        <v>44.1149904500001</v>
+        <v>44.11499044999993</v>
       </c>
       <c r="I66" t="n">
         <v>35</v>
@@ -6724,7 +6724,7 @@
         <v>0.42</v>
       </c>
       <c r="L66" t="n">
-        <v>78.69499045000011</v>
+        <v>78.69499044999993</v>
       </c>
       <c r="M66" t="n">
         <v>37.37499999999999</v>
@@ -6745,10 +6745,10 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>41.31999045000011</v>
+        <v>41.31999044999994</v>
       </c>
       <c r="T66" t="n">
-        <v>2.563049427000006</v>
+        <v>2.563049426999996</v>
       </c>
       <c r="U66" t="n">
         <v>15.83333333333333</v>
@@ -6783,7 +6783,7 @@
         <v>0.012</v>
       </c>
       <c r="H67" t="n">
-        <v>41.31999045000011</v>
+        <v>41.31999044999994</v>
       </c>
       <c r="I67" t="n">
         <v>35</v>
@@ -6795,7 +6795,7 @@
         <v>0.42</v>
       </c>
       <c r="L67" t="n">
-        <v>75.89999045000012</v>
+        <v>75.89999044999995</v>
       </c>
       <c r="M67" t="n">
         <v>37.37499999999999</v>
@@ -6816,10 +6816,10 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>38.52499045000013</v>
+        <v>38.52499044999995</v>
       </c>
       <c r="T67" t="n">
-        <v>2.395349427000007</v>
+        <v>2.395349426999997</v>
       </c>
       <c r="U67" t="n">
         <v>15.83333333333333</v>
@@ -6854,7 +6854,7 @@
         <v>0.012</v>
       </c>
       <c r="H68" t="n">
-        <v>38.52499045000013</v>
+        <v>38.52499044999995</v>
       </c>
       <c r="I68" t="n">
         <v>35</v>
@@ -6866,7 +6866,7 @@
         <v>0.42</v>
       </c>
       <c r="L68" t="n">
-        <v>73.10499045000013</v>
+        <v>73.10499044999996</v>
       </c>
       <c r="M68" t="n">
         <v>37.37499999999999</v>
@@ -6887,10 +6887,10 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>35.72999045000014</v>
+        <v>35.72999044999997</v>
       </c>
       <c r="T68" t="n">
-        <v>2.227649427000008</v>
+        <v>2.227649426999998</v>
       </c>
       <c r="U68" t="n">
         <v>15.83333333333333</v>
@@ -6925,7 +6925,7 @@
         <v>0.012</v>
       </c>
       <c r="H69" t="n">
-        <v>35.72999045000014</v>
+        <v>35.72999044999997</v>
       </c>
       <c r="I69" t="n">
         <v>35</v>
@@ -6937,7 +6937,7 @@
         <v>0.42</v>
       </c>
       <c r="L69" t="n">
-        <v>70.30999045000014</v>
+        <v>70.30999044999997</v>
       </c>
       <c r="M69" t="n">
         <v>37.37499999999999</v>
@@ -6958,10 +6958,10 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>32.93499045000015</v>
+        <v>32.93499044999998</v>
       </c>
       <c r="T69" t="n">
-        <v>2.059949427000009</v>
+        <v>2.059949426999998</v>
       </c>
       <c r="U69" t="n">
         <v>15.83333333333333</v>
@@ -6996,7 +6996,7 @@
         <v>0.012</v>
       </c>
       <c r="H70" t="n">
-        <v>32.93499045000015</v>
+        <v>32.93499044999998</v>
       </c>
       <c r="I70" t="n">
         <v>35</v>
@@ -7008,7 +7008,7 @@
         <v>0.42</v>
       </c>
       <c r="L70" t="n">
-        <v>67.51499045000016</v>
+        <v>67.51499044999998</v>
       </c>
       <c r="M70" t="n">
         <v>37.37499999999999</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>30.13999045000016</v>
+        <v>30.13999044999999</v>
       </c>
       <c r="T70" t="n">
-        <v>1.892249427000009</v>
+        <v>1.892249426999999</v>
       </c>
       <c r="U70" t="n">
         <v>15.83333333333333</v>
@@ -7067,7 +7067,7 @@
         <v>0.012</v>
       </c>
       <c r="H71" t="n">
-        <v>30.13999045000016</v>
+        <v>30.13999044999999</v>
       </c>
       <c r="I71" t="n">
         <v>35</v>
@@ -7079,7 +7079,7 @@
         <v>0.42</v>
       </c>
       <c r="L71" t="n">
-        <v>64.71999045000017</v>
+        <v>64.71999045</v>
       </c>
       <c r="M71" t="n">
         <v>37.37499999999999</v>
@@ -7100,10 +7100,10 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>27.34499045000018</v>
+        <v>27.34499045</v>
       </c>
       <c r="T71" t="n">
-        <v>1.72454942700001</v>
+        <v>1.724549427</v>
       </c>
       <c r="U71" t="n">
         <v>15.83333333333333</v>
@@ -7138,7 +7138,7 @@
         <v>0.012</v>
       </c>
       <c r="H72" t="n">
-        <v>27.34499045000018</v>
+        <v>27.34499045</v>
       </c>
       <c r="I72" t="n">
         <v>35</v>
@@ -7150,7 +7150,7 @@
         <v>0.42</v>
       </c>
       <c r="L72" t="n">
-        <v>61.92499045000017</v>
+        <v>61.92499045</v>
       </c>
       <c r="M72" t="n">
         <v>37.37499999999999</v>
@@ -7171,10 +7171,10 @@
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>24.54999045000018</v>
+        <v>24.54999045000001</v>
       </c>
       <c r="T72" t="n">
-        <v>1.55684942700001</v>
+        <v>1.556849427</v>
       </c>
       <c r="U72" t="n">
         <v>15.83333333333333</v>
@@ -7209,7 +7209,7 @@
         <v>0.012</v>
       </c>
       <c r="H73" t="n">
-        <v>24.54999045000018</v>
+        <v>24.54999045000001</v>
       </c>
       <c r="I73" t="n">
         <v>35</v>
@@ -7221,7 +7221,7 @@
         <v>0.42</v>
       </c>
       <c r="L73" t="n">
-        <v>59.12999045000018</v>
+        <v>59.12999045000001</v>
       </c>
       <c r="M73" t="n">
         <v>37.37499999999999</v>
@@ -7242,10 +7242,10 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>21.75499045000019</v>
+        <v>21.75499045000002</v>
       </c>
       <c r="T73" t="n">
-        <v>1.389149427000011</v>
+        <v>1.389149427000001</v>
       </c>
       <c r="U73" t="n">
         <v>15.83333333333333</v>
@@ -8695,10 +8695,10 @@
         <v>56.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>56.03720000000001</v>
+        <v>56.0372</v>
       </c>
       <c r="N19" t="n">
-        <v>56.03720000000001</v>
+        <v>56.0372</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -9962,7 +9962,7 @@
         <v>100.87725</v>
       </c>
       <c r="F6" t="n">
-        <v>36.23949349200005</v>
+        <v>36.23949349199999</v>
       </c>
       <c r="G6" t="n">
         <v>82</v>
@@ -10004,7 +10004,7 @@
         <v>102</v>
       </c>
       <c r="F7" t="n">
-        <v>27.73799312400009</v>
+        <v>27.73799312399997</v>
       </c>
       <c r="G7" t="n">
         <v>82</v>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0.99</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.99</v>
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0.97</v>
@@ -10637,7 +10637,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>0.97</v>
@@ -11368,7 +11368,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>55.29499045000006</v>
+        <v>55.29499044999989</v>
       </c>
       <c r="G28" t="n">
         <v>55.2945205479452</v>
@@ -13080,7 +13080,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>55.29499045000006</v>
+        <v>55.29499044999989</v>
       </c>
       <c r="G64" t="n">
         <v>120</v>
@@ -13511,7 +13511,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>52.49999045000006</v>
+        <v>52.49999044999989</v>
       </c>
       <c r="G73" t="n">
         <v>120</v>
@@ -22641,7 +22641,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>5.684341886080801e-14</v>
       </c>
     </row>
     <row r="9">
@@ -22661,7 +22661,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="10">
@@ -22741,7 +22741,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9999999999999997</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -22841,7 +22841,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>505.2292200000001</v>
+        <v>505.22922</v>
       </c>
     </row>
     <row r="19">
@@ -22861,7 +22861,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>135.6853910070003</v>
+        <v>135.6853910070001</v>
       </c>
     </row>
     <row r="20">
@@ -22941,7 +22941,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21.75499045000019</v>
+        <v>21.75499045000002</v>
       </c>
     </row>
     <row r="24">

--- a/results/stress/P3_isru_zbo_adapted_MANDATORY_STRESS/results.xlsx
+++ b/results/stress/P3_isru_zbo_adapted_MANDATORY_STRESS/results.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TerraPlan export</t>
+          <t>Выгрузка TerraPlan, версия</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>план (plan_id)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>сценарий (scenario_id)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -465,96 +465,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feasible</t>
+          <t>план исполним</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit:fuel</t>
+          <t>жёстких нарушений / отклонений от ориентиров / предупреждений</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>0 / 0 / 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit:money</t>
+          <t>единица: fuel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mln conventional units, constant 2035 prices</t>
+          <t>т</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit:capacity</t>
+          <t>единица: money</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t/year</t>
+          <t>млн у.е., постоянные цены 2035 г.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit:reservation_rate</t>
+          <t>единица: capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mln per (t/year)</t>
+          <t>т/год</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit:service_level</t>
+          <t>единица: reservation_rate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share 0..1</t>
+          <t>млн у.е. за (т/год)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>unit:time_step</t>
+          <t>единица: service_level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>calendar month</t>
+          <t>доля 0..1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>единица: time_step</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>календарный месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>периоды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2035-01 … 2040-12, шаг — календарный месяц; подготовительный период до 2035-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>листы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yearly_balance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>годовой баланс: спрос, выдача, дефицит, уровни сервиса, поступление, потери, запасы, 45-дневный резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory_trace</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>помесячный материальный баланс и стоимость хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>source_schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>по источникам и годам: резерв, заказ, план/факт поставки, цена, оплачиваемый объём (take-or-pay), платежи</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>financial_breakdown</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>по годам: закупка, резервирование, хранение, постоянный OPEX, CAPEX, итого, PV, накопленный CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>constraint_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нарушения: правило, строгость, год, месяц, источник, факт, лимит, превышение, сообщение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>constraint_matrix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>матрица проверок: каждое правило × год, включая выполненные</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_schedule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>календарь поставок: месяц поставки, месяц размещения заказа, срок поставки, допустимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>итоговые показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>инвестиционные решения: даты опциона, реализации, ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>реестр допущений TEAM_ASSUMPTION: значение, единица, статус, диапазон, обоснование</t>
         </is>
       </c>
     </row>
@@ -774,7 +918,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>share per year (real)</t>
+          <t>доля в год (реальная ставка)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -789,7 +933,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real discount rate for long-lived infrastructure with technology risk. Not given by the organizer. Used identically for all alternatives; sensitivity 0–12 % in experiments/run_sensitivity.py.
+          <t xml:space="preserve">Реальная ставка дисконтирования для долгоживущей инфраструктуры с технологическим риском. Организатором не задана. Применяется одинаково ко всем альтернативам; чувствительность 0–12 % в experiments/run_sensitivity.py.
 </t>
         </is>
       </c>
@@ -807,7 +951,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -822,7 +966,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year; PV factor = 1/(1+r)^(year-2035).</t>
+          <t>Годовые денежные потоки датируются началом каждого года; коэффициент приведения = 1/(1+r)^(год − 2035).</t>
         </is>
       </c>
     </row>
@@ -839,7 +983,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>enum start|mid|end</t>
+          <t>перечисление start|mid|end</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -854,7 +998,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year (exponent year-2035); mid/end-year conventions available and applied identically to all alternatives.</t>
+          <t>Момент внутри года, к которому отнесён годовой поток — начало (показатель степени год − 2035), середина (+0,5) или конец (+1); одинаково для всех альтернатив.</t>
         </is>
       </c>
     </row>
@@ -871,7 +1015,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -886,7 +1030,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earliest order date of the preparatory period (Earth-Core needs 12 months before 2035-01).</t>
+          <t>Самая ранняя дата заказа в подготовительном периоде (Earth-Core требует 12 месяцев до 2035-01).</t>
         </is>
       </c>
     </row>
@@ -903,7 +1047,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>enum min|max|mean</t>
+          <t>перечисление min|max|mean</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -918,7 +1062,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conservative end of the organizer lead-time ranges (Earth-New 24 months, ISRU 2 months).</t>
+          <t>Консервативный край диапазонов сроков поставки организатора (Earth-New 24 месяца, ISRU 2 месяца).</t>
         </is>
       </c>
     </row>
@@ -935,7 +1079,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>недель</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -950,7 +1094,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>365/12/7. Week lead times converted with ceil(weeks/4.345) -&gt; Emergency 6 weeks = 2 months.</t>
+          <t>365/12/7. Сроки в неделях переводятся как ceil(недели/4,345) -&gt; Emergency 6 недель = 2 месяца.</t>
         </is>
       </c>
     </row>
@@ -967,7 +1111,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -982,7 +1126,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>365/12; day-denominated lead times converted with ceil.</t>
+          <t>365/12; сроки в днях переводятся с округлением вверх.</t>
         </is>
       </c>
     </row>
@@ -999,7 +1143,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1014,7 +1158,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Case gives no ZBO build time; modernization active from the CAPEX month. Varied in sensitivity.</t>
+          <t>Кейс не задаёт срок модернизации ZBO; она считается действующей с месяца оплаты CAPEX. Варьируется в анализе чувствительности.</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1175,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1046,7 +1190,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The 18–24 month Earth-New lead time is read as decision-to-first-delivery; orders are placed during preparation.</t>
+          <t>Срок Earth-New 18–24 месяца трактуется как время от решения до первой поставки; заказы размещаются в период подготовки, после ввода дополнительный срок заказа 0 месяцев.</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1207,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1078,7 +1222,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunar-ISRU available from 2038 once CAPEX is financed before 2038.</t>
+          <t>Lunar-ISRU доступен с 2038 года при финансировании CAPEX до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1239,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1110,7 +1254,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAPEX 1250 must be financed before 2038.</t>
+          <t>CAPEX 1 250 млн должен быть профинансирован до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1271,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>map source_id -&gt; investment_id</t>
+          <t>отображение source_id -&gt; investment_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1142,7 +1286,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Earth-New capacity requires the exercised option; Lunar-ISRU requires the pilot CAPEX.</t>
+          <t>Мощность Earth-New требует реализованного опциона; Lunar-ISRU — CAPEX пилотного производства.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1303,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>map investment_id -&gt; storage_id</t>
+          <t>отображение investment_id -&gt; storage_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1174,7 +1318,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBO modernization switches the active storage mode (capacity 120 t, losses 1.2 %, OPEX 12/yr).</t>
+          <t>Модернизация ZBO переключает активный режим хранилища (ёмкость 120 т, потери 1,2 %, OPEX 12 млн/год).</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1335,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share of annual total demand</t>
+          <t>доля годового общего спроса</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1206,7 +1350,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emergency counts as the base channel in a year when its ordered volume exceeds 20 % of that year's demand.</t>
+          <t>Emergency считается базовым каналом в году, когда заказанный у него объём превышает 20 % спроса этого года.</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1367,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1238,7 +1382,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Average physical stock per month = (I_start + I_end)/2; holding = 0.72 x average x 1/12.</t>
+          <t>Средний физический запас за месяц = (I_start + I_end)/2; стоимость хранения = 0,72 × средний запас × 1/12.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1399,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,7 +1414,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hard violation when end-of-month stock &gt; capacity; warning when stock after inflow (before withdrawals) &gt; capacity.</t>
+          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1431,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1302,7 +1446,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contracted Emergency reserve counts only if stock covers demand during the 6-week lead time and reserved Emergency capacity &gt;= R_y.</t>
+          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1463,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1334,7 +1478,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The preparatory-period purchase pays the source reservation rate on the purchased tonnage for one year; booked in 2035.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1495,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1366,7 +1510,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holding cost charged from 2035-01; storage time in the preparatory period (&lt; 1 month) is not charged.</t>
+          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1527,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1398,7 +1542,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Organizer convention — uniform demand within the year, 365 days.</t>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
         </is>
       </c>
     </row>
@@ -11424,7 +11568,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11437,7 +11581,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11473,7 +11617,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11486,7 +11630,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11522,7 +11666,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11535,7 +11679,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11715,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11584,7 +11728,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11764,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11633,7 +11777,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11813,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -11682,7 +11826,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -13928,7 +14072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M155"/>
+  <dimension ref="A1:N155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13997,6 +14141,11 @@
           <t>lead_time_ok</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lead_time_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14052,6 +14201,11 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14107,6 +14261,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14162,6 +14321,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14217,6 +14381,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14272,6 +14441,11 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14327,6 +14501,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14382,6 +14561,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14437,6 +14621,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14492,6 +14681,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14547,6 +14741,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14602,6 +14801,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14657,6 +14861,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14712,6 +14921,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14767,6 +14981,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14822,6 +15041,11 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14877,6 +15101,11 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14932,6 +15161,11 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14987,6 +15221,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -15042,6 +15281,11 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15097,6 +15341,11 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15152,6 +15401,11 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15207,6 +15461,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15262,6 +15521,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15317,6 +15581,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15372,6 +15641,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15427,6 +15701,11 @@
       <c r="M27" t="b">
         <v>1</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15482,6 +15761,11 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15537,6 +15821,11 @@
       <c r="M29" t="b">
         <v>1</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15592,6 +15881,11 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15647,6 +15941,11 @@
       <c r="M31" t="b">
         <v>1</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15702,6 +16001,11 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15757,6 +16061,11 @@
       <c r="M33" t="b">
         <v>1</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15812,6 +16121,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15867,6 +16181,11 @@
       <c r="M35" t="b">
         <v>1</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -15922,6 +16241,11 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -15977,6 +16301,11 @@
       <c r="M37" t="b">
         <v>1</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -16032,6 +16361,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16087,6 +16421,11 @@
       <c r="M39" t="b">
         <v>1</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -16142,6 +16481,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16197,6 +16541,11 @@
       <c r="M41" t="b">
         <v>1</v>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -16252,6 +16601,11 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16307,6 +16661,11 @@
       <c r="M43" t="b">
         <v>1</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -16362,6 +16721,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16417,6 +16781,11 @@
       <c r="M45" t="b">
         <v>1</v>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -16472,6 +16841,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16527,6 +16901,11 @@
       <c r="M47" t="b">
         <v>1</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -16582,6 +16961,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16637,6 +17021,11 @@
       <c r="M49" t="b">
         <v>1</v>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -16692,6 +17081,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16747,6 +17141,11 @@
       <c r="M51" t="b">
         <v>1</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -16802,6 +17201,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -16857,6 +17261,11 @@
       <c r="M53" t="b">
         <v>1</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -16912,6 +17321,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -16967,6 +17381,11 @@
       <c r="M55" t="b">
         <v>1</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17022,6 +17441,11 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17077,6 +17501,11 @@
       <c r="M57" t="b">
         <v>1</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -17132,6 +17561,11 @@
       <c r="M58" t="b">
         <v>1</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17187,6 +17621,11 @@
       <c r="M59" t="b">
         <v>1</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -17242,6 +17681,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17297,6 +17741,11 @@
       <c r="M61" t="b">
         <v>1</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -17352,6 +17801,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17407,6 +17861,11 @@
       <c r="M63" t="b">
         <v>1</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17462,6 +17921,11 @@
       <c r="M64" t="b">
         <v>1</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17517,6 +17981,11 @@
       <c r="M65" t="b">
         <v>1</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17572,6 +18041,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17627,6 +18101,11 @@
       <c r="M67" t="b">
         <v>1</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -17682,6 +18161,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17737,6 +18221,11 @@
       <c r="M69" t="b">
         <v>1</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -17792,6 +18281,11 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -17847,6 +18341,11 @@
       <c r="M71" t="b">
         <v>1</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -17902,6 +18401,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -17957,6 +18461,11 @@
       <c r="M73" t="b">
         <v>1</v>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18012,6 +18521,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18067,6 +18581,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18122,6 +18641,11 @@
       <c r="M76" t="b">
         <v>1</v>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -18177,6 +18701,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18232,6 +18761,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18287,6 +18821,11 @@
       <c r="M79" t="b">
         <v>1</v>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -18342,6 +18881,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -18397,6 +18941,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -18452,6 +19001,11 @@
       <c r="M82" t="b">
         <v>1</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -18507,6 +19061,11 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18562,6 +19121,11 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -18617,6 +19181,11 @@
       <c r="M85" t="b">
         <v>1</v>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -18672,6 +19241,11 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -18727,6 +19301,11 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -18782,6 +19361,11 @@
       <c r="M88" t="b">
         <v>1</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -18837,6 +19421,11 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -18892,6 +19481,11 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -18947,6 +19541,11 @@
       <c r="M91" t="b">
         <v>1</v>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -19002,6 +19601,11 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19057,6 +19661,11 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19112,6 +19721,11 @@
       <c r="M94" t="b">
         <v>1</v>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -19167,6 +19781,11 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -19222,6 +19841,11 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19277,6 +19901,11 @@
       <c r="M97" t="b">
         <v>1</v>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -19332,6 +19961,11 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -19387,6 +20021,11 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19442,6 +20081,11 @@
       <c r="M100" t="b">
         <v>1</v>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -19497,6 +20141,11 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19552,6 +20201,11 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19607,6 +20261,11 @@
       <c r="M103" t="b">
         <v>1</v>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19662,6 +20321,11 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -19717,6 +20381,11 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19772,6 +20441,11 @@
       <c r="M106" t="b">
         <v>1</v>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -19827,6 +20501,11 @@
       <c r="M107" t="b">
         <v>1</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -19882,6 +20561,11 @@
       <c r="M108" t="b">
         <v>1</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -19937,6 +20621,11 @@
       <c r="M109" t="b">
         <v>1</v>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -19992,6 +20681,11 @@
       <c r="M110" t="b">
         <v>1</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -20047,6 +20741,11 @@
       <c r="M111" t="b">
         <v>1</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -20102,6 +20801,11 @@
       <c r="M112" t="b">
         <v>1</v>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -20157,6 +20861,11 @@
       <c r="M113" t="b">
         <v>1</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -20212,6 +20921,11 @@
       <c r="M114" t="b">
         <v>1</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -20267,6 +20981,11 @@
       <c r="M115" t="b">
         <v>1</v>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -20322,6 +21041,11 @@
       <c r="M116" t="b">
         <v>1</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -20377,6 +21101,11 @@
       <c r="M117" t="b">
         <v>1</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -20432,6 +21161,11 @@
       <c r="M118" t="b">
         <v>1</v>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -20487,6 +21221,11 @@
       <c r="M119" t="b">
         <v>1</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20542,6 +21281,11 @@
       <c r="M120" t="b">
         <v>1</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20597,6 +21341,11 @@
       <c r="M121" t="b">
         <v>1</v>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -20652,6 +21401,11 @@
       <c r="M122" t="b">
         <v>1</v>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20707,6 +21461,11 @@
       <c r="M123" t="b">
         <v>1</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -20762,6 +21521,11 @@
       <c r="M124" t="b">
         <v>1</v>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -20817,6 +21581,11 @@
       <c r="M125" t="b">
         <v>1</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -20872,6 +21641,11 @@
       <c r="M126" t="b">
         <v>1</v>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -20927,6 +21701,11 @@
       <c r="M127" t="b">
         <v>1</v>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -20982,6 +21761,11 @@
       <c r="M128" t="b">
         <v>1</v>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21037,6 +21821,11 @@
       <c r="M129" t="b">
         <v>1</v>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -21092,6 +21881,11 @@
       <c r="M130" t="b">
         <v>1</v>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -21147,6 +21941,11 @@
       <c r="M131" t="b">
         <v>1</v>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -21202,6 +22001,11 @@
       <c r="M132" t="b">
         <v>1</v>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21257,6 +22061,11 @@
       <c r="M133" t="b">
         <v>1</v>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -21312,6 +22121,11 @@
       <c r="M134" t="b">
         <v>1</v>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21367,6 +22181,11 @@
       <c r="M135" t="b">
         <v>1</v>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -21422,6 +22241,11 @@
       <c r="M136" t="b">
         <v>1</v>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -21477,6 +22301,11 @@
       <c r="M137" t="b">
         <v>1</v>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -21532,6 +22361,11 @@
       <c r="M138" t="b">
         <v>1</v>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -21587,6 +22421,11 @@
       <c r="M139" t="b">
         <v>1</v>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -21642,6 +22481,11 @@
       <c r="M140" t="b">
         <v>1</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -21697,6 +22541,11 @@
       <c r="M141" t="b">
         <v>1</v>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -21752,6 +22601,11 @@
       <c r="M142" t="b">
         <v>1</v>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -21807,6 +22661,11 @@
       <c r="M143" t="b">
         <v>1</v>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -21862,6 +22721,11 @@
       <c r="M144" t="b">
         <v>1</v>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -21917,6 +22781,11 @@
       <c r="M145" t="b">
         <v>1</v>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -21972,6 +22841,11 @@
       <c r="M146" t="b">
         <v>1</v>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -22027,6 +22901,11 @@
       <c r="M147" t="b">
         <v>1</v>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -22082,6 +22961,11 @@
       <c r="M148" t="b">
         <v>1</v>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -22137,6 +23021,11 @@
       <c r="M149" t="b">
         <v>1</v>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -22192,6 +23081,11 @@
       <c r="M150" t="b">
         <v>1</v>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -22247,6 +23141,11 @@
       <c r="M151" t="b">
         <v>1</v>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -22302,6 +23201,11 @@
       <c r="M152" t="b">
         <v>1</v>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -22357,6 +23261,11 @@
       <c r="M153" t="b">
         <v>1</v>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -22412,6 +23321,11 @@
       <c r="M154" t="b">
         <v>1</v>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -22466,6 +23380,11 @@
       </c>
       <c r="M155" t="b">
         <v>1</v>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/results/stress/P3_isru_zbo_adapted_MANDATORY_STRESS/results.xlsx
+++ b/results/stress/P3_isru_zbo_adapted_MANDATORY_STRESS/results.xlsx
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,6 +1543,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -11557,18 +11590,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11581,7 +11614,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11606,18 +11639,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11630,7 +11663,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11655,18 +11688,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11679,7 +11712,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11704,18 +11737,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11728,7 +11761,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11753,18 +11786,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11777,7 +11810,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11802,18 +11835,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -11826,7 +11859,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11986,7 +12019,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -12010,7 +12043,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12254,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -12245,7 +12278,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12456,11 +12489,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>35.44551565000008</v>
+        <v>27.71964825000006</v>
       </c>
       <c r="G48" t="n">
         <v>70</v>
@@ -12480,7 +12513,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12789,7 +12822,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -12813,7 +12846,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13253,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -13244,7 +13277,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13651,7 +13684,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -13675,7 +13708,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/stress/P3_isru_zbo_adapted_MANDATORY_STRESS/results.xlsx
+++ b/results/stress/P3_isru_zbo_adapted_MANDATORY_STRESS/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,6 +1575,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/stress/P3_isru_zbo_adapted_MANDATORY_STRESS/results.xlsx
+++ b/results/stress/P3_isru_zbo_adapted_MANDATORY_STRESS/results.xlsx
@@ -7538,7 +7538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7647,6 +7647,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7722,6 +7727,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7797,6 +7805,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7872,6 +7883,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7947,6 +7961,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8022,6 +8039,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8097,6 +8117,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8172,6 +8195,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8247,6 +8273,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8322,6 +8351,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8397,6 +8429,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8472,6 +8507,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8547,6 +8585,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8622,6 +8663,9 @@
       <c r="U14" t="n">
         <v>2.6922</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8697,6 +8741,9 @@
       <c r="U15" t="n">
         <v>0</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8772,6 +8819,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8847,6 +8897,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8922,6 +8975,9 @@
       <c r="U18" t="n">
         <v>85.5</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8997,6 +9053,9 @@
       <c r="U19" t="n">
         <v>8.4057</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9072,6 +9131,9 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9147,6 +9209,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9222,6 +9287,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9297,6 +9365,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9372,6 +9443,9 @@
       <c r="U24" t="n">
         <v>15.37725</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9447,6 +9521,9 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9522,6 +9599,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9597,6 +9677,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9672,6 +9755,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9747,6 +9833,9 @@
       <c r="U29" t="n">
         <v>16.5</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9822,6 +9911,9 @@
       <c r="U30" t="n">
         <v>0</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9897,6 +9989,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9970,6 +10065,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9984,7 +10082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10048,6 +10146,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10090,6 +10193,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10132,6 +10238,9 @@
       <c r="L3" t="n">
         <v>1250</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10174,6 +10283,9 @@
       <c r="L4" t="n">
         <v>1430</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10216,6 +10328,9 @@
       <c r="L5" t="n">
         <v>1430</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10258,6 +10373,9 @@
       <c r="L6" t="n">
         <v>1430</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10299,6 +10417,9 @@
       </c>
       <c r="L7" t="n">
         <v>1430</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23530,7 +23651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23968,11 +24089,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -23988,11 +24109,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21.75499045000002</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -24008,11 +24129,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>21.75499045000002</v>
       </c>
     </row>
     <row r="25">
@@ -24028,7 +24149,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -24048,7 +24169,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -24068,11 +24189,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -24088,11 +24209,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>80</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -24108,10 +24229,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>80</v>
       </c>
     </row>

--- a/results/stress/P3_isru_zbo_adapted_MANDATORY_STRESS/results.xlsx
+++ b/results/stress/P3_isru_zbo_adapted_MANDATORY_STRESS/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -870,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,7 +1396,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1414,24 +1416,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1441,29 +1443,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1473,29 +1475,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1505,176 +1507,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2411,6 +2556,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2483,6 +2638,12 @@
         <v>0.7520604900000002</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2554,6 +2715,12 @@
         <v>0.7767183900000002</v>
       </c>
       <c r="U3" t="n">
+        <v>21.48412233333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2625,6 +2792,12 @@
         <v>0.8013762900000003</v>
       </c>
       <c r="U4" t="n">
+        <v>21.89508733333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2696,6 +2869,12 @@
         <v>0.8260341900000004</v>
       </c>
       <c r="U5" t="n">
+        <v>22.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2767,6 +2946,12 @@
         <v>0.8506920900000003</v>
       </c>
       <c r="U6" t="n">
+        <v>22.71701733333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2838,6 +3023,12 @@
         <v>0.8753499900000005</v>
       </c>
       <c r="U7" t="n">
+        <v>23.12798233333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2909,6 +3100,12 @@
         <v>0.9000078900000005</v>
       </c>
       <c r="U8" t="n">
+        <v>23.53894733333334</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2980,6 +3177,12 @@
         <v>0.9246657900000006</v>
       </c>
       <c r="U9" t="n">
+        <v>23.94991233333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3051,6 +3254,12 @@
         <v>0.9493236900000007</v>
       </c>
       <c r="U10" t="n">
+        <v>24.36087733333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3122,6 +3331,12 @@
         <v>0.973981590000001</v>
       </c>
       <c r="U11" t="n">
+        <v>24.77184233333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3193,6 +3408,12 @@
         <v>0.9986394900000012</v>
       </c>
       <c r="U12" t="n">
+        <v>25.18280733333335</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3264,6 +3485,12 @@
         <v>1.023297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>25.59377233333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3335,6 +3562,12 @@
         <v>1.051037512500002</v>
       </c>
       <c r="U14" t="n">
+        <v>29.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3406,6 +3639,12 @@
         <v>1.081859857500002</v>
       </c>
       <c r="U15" t="n">
+        <v>29.95451716666669</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3477,6 +3716,12 @@
         <v>1.112682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>30.46822291666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3548,6 +3793,12 @@
         <v>1.143504547500002</v>
       </c>
       <c r="U17" t="n">
+        <v>30.98192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3619,6 +3870,12 @@
         <v>1.174326892500001</v>
       </c>
       <c r="U18" t="n">
+        <v>31.49563441666669</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3690,6 +3947,12 @@
         <v>1.205149237500002</v>
       </c>
       <c r="U19" t="n">
+        <v>32.00934016666669</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3761,6 +4024,12 @@
         <v>1.235971582500002</v>
       </c>
       <c r="U20" t="n">
+        <v>32.5230459166667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3832,6 +4101,12 @@
         <v>1.266793927500003</v>
       </c>
       <c r="U21" t="n">
+        <v>33.0367516666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3903,6 +4178,12 @@
         <v>1.297616272500003</v>
       </c>
       <c r="U22" t="n">
+        <v>33.55045741666671</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3974,6 +4255,12 @@
         <v>1.328438617500003</v>
       </c>
       <c r="U23" t="n">
+        <v>34.06416316666672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4045,6 +4332,12 @@
         <v>1.359260962500004</v>
       </c>
       <c r="U24" t="n">
+        <v>34.57786891666672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4116,6 +4409,12 @@
         <v>1.390083307500004</v>
       </c>
       <c r="U25" t="n">
+        <v>35.09157466666673</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4187,6 +4486,12 @@
         <v>1.426968181250004</v>
       </c>
       <c r="U26" t="n">
+        <v>39.97403137500007</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4258,6 +4563,12 @@
         <v>1.469915583750004</v>
       </c>
       <c r="U27" t="n">
+        <v>40.68982141666674</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4329,6 +4640,12 @@
         <v>1.512862986250004</v>
       </c>
       <c r="U28" t="n">
+        <v>41.4056114583334</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4400,6 +4717,12 @@
         <v>1.555810388750004</v>
       </c>
       <c r="U29" t="n">
+        <v>42.12140150000007</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4471,6 +4794,12 @@
         <v>1.598757791250004</v>
       </c>
       <c r="U30" t="n">
+        <v>42.83719154166673</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4542,6 +4871,12 @@
         <v>1.641705193750004</v>
       </c>
       <c r="U31" t="n">
+        <v>43.5529815833334</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4613,6 +4948,12 @@
         <v>1.701808232000004</v>
       </c>
       <c r="U32" t="n">
+        <v>44.84062615000006</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4684,6 +5025,12 @@
         <v>1.779066906000004</v>
       </c>
       <c r="U33" t="n">
+        <v>46.12827071666673</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4755,6 +5102,12 @@
         <v>1.856325580000004</v>
       </c>
       <c r="U34" t="n">
+        <v>47.4159152833334</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4826,6 +5179,12 @@
         <v>1.933584254000004</v>
       </c>
       <c r="U35" t="n">
+        <v>48.70355985000008</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4897,6 +5256,12 @@
         <v>2.010842928000005</v>
       </c>
       <c r="U36" t="n">
+        <v>49.99120441666675</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4968,6 +5333,12 @@
         <v>2.088101602000005</v>
       </c>
       <c r="U37" t="n">
+        <v>51.27884898333342</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5039,6 +5410,12 @@
         <v>2.015692823000005</v>
       </c>
       <c r="U38" t="n">
+        <v>55.70257845000008</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5110,6 +5487,12 @@
         <v>1.793616591000005</v>
       </c>
       <c r="U39" t="n">
+        <v>52.00130791666675</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5181,6 +5564,12 @@
         <v>1.734560359000004</v>
       </c>
       <c r="U40" t="n">
+        <v>53.73403738333341</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5252,6 +5641,12 @@
         <v>1.838524127000005</v>
       </c>
       <c r="U41" t="n">
+        <v>55.46676685000008</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5323,6 +5718,12 @@
         <v>1.942487895000005</v>
       </c>
       <c r="U42" t="n">
+        <v>57.19949631666675</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5394,6 +5795,12 @@
         <v>2.046451663000004</v>
       </c>
       <c r="U43" t="n">
+        <v>58.93222578333341</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5465,6 +5872,12 @@
         <v>2.150415431000005</v>
       </c>
       <c r="U44" t="n">
+        <v>60.66495525000008</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5536,6 +5949,12 @@
         <v>2.254379199000005</v>
       </c>
       <c r="U45" t="n">
+        <v>62.39768471666675</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5607,6 +6026,12 @@
         <v>2.358342967000005</v>
       </c>
       <c r="U46" t="n">
+        <v>64.13041418333341</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5678,6 +6103,12 @@
         <v>2.462306735000005</v>
       </c>
       <c r="U47" t="n">
+        <v>65.86314365000008</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5749,6 +6180,12 @@
         <v>2.566270503000005</v>
       </c>
       <c r="U48" t="n">
+        <v>67.59587311666675</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5820,6 +6257,12 @@
         <v>2.670234271000005</v>
       </c>
       <c r="U49" t="n">
+        <v>69.32860258333342</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5891,6 +6334,12 @@
         <v>2.747027958000005</v>
       </c>
       <c r="U50" t="n">
+        <v>76.86399601666676</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5962,6 +6411,12 @@
         <v>2.796651564000004</v>
       </c>
       <c r="U51" t="n">
+        <v>77.69105611666674</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6033,6 +6488,12 @@
         <v>2.846275170000003</v>
       </c>
       <c r="U52" t="n">
+        <v>78.51811621666673</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6104,6 +6565,12 @@
         <v>2.895898776000001</v>
       </c>
       <c r="U53" t="n">
+        <v>79.34517631666671</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6175,6 +6642,12 @@
         <v>2.945522382</v>
       </c>
       <c r="U54" t="n">
+        <v>80.17223641666669</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6246,6 +6719,12 @@
         <v>2.995145988</v>
       </c>
       <c r="U55" t="n">
+        <v>80.99929651666667</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6317,6 +6796,12 @@
         <v>3.044769593999999</v>
       </c>
       <c r="U56" t="n">
+        <v>81.82635661666666</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6388,6 +6873,12 @@
         <v>3.094393199999998</v>
       </c>
       <c r="U57" t="n">
+        <v>82.65341671666664</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6459,6 +6950,12 @@
         <v>3.144016805999997</v>
       </c>
       <c r="U58" t="n">
+        <v>83.48047681666662</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6530,6 +7027,12 @@
         <v>3.193640411999996</v>
       </c>
       <c r="U59" t="n">
+        <v>84.30753691666661</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6601,6 +7104,12 @@
         <v>3.243264017999995</v>
       </c>
       <c r="U60" t="n">
+        <v>85.13459701666659</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6672,6 +7181,12 @@
         <v>3.292887623999993</v>
       </c>
       <c r="U61" t="n">
+        <v>85.96165711666657</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6743,6 +7258,12 @@
         <v>3.233849426999993</v>
       </c>
       <c r="U62" t="n">
+        <v>89.87499044999988</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6814,6 +7335,12 @@
         <v>3.066149426999994</v>
       </c>
       <c r="U63" t="n">
+        <v>87.07999044999988</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6885,6 +7412,12 @@
         <v>2.898449426999994</v>
       </c>
       <c r="U64" t="n">
+        <v>84.2849904499999</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6956,6 +7489,12 @@
         <v>2.730749426999995</v>
       </c>
       <c r="U65" t="n">
+        <v>81.48999044999991</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7027,6 +7566,12 @@
         <v>2.563049426999996</v>
       </c>
       <c r="U66" t="n">
+        <v>78.69499044999992</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7098,6 +7643,12 @@
         <v>2.395349426999997</v>
       </c>
       <c r="U67" t="n">
+        <v>75.89999044999993</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7169,6 +7720,12 @@
         <v>2.227649426999998</v>
       </c>
       <c r="U68" t="n">
+        <v>73.10499044999995</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7240,6 +7797,12 @@
         <v>2.059949426999998</v>
       </c>
       <c r="U69" t="n">
+        <v>70.30999044999996</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7311,6 +7874,12 @@
         <v>1.892249426999999</v>
       </c>
       <c r="U70" t="n">
+        <v>67.51499044999997</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7382,6 +7951,12 @@
         <v>1.724549427</v>
       </c>
       <c r="U71" t="n">
+        <v>64.71999044999998</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7453,6 +8028,12 @@
         <v>1.556849427</v>
       </c>
       <c r="U72" t="n">
+        <v>61.92499045</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7524,6 +8105,12 @@
         <v>1.389149427000001</v>
       </c>
       <c r="U73" t="n">
+        <v>59.12999045000001</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10173,7 +10760,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65214728000001</v>
+        <v>11.02201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10182,13 +10769,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -10454,7 +11041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12280,7 +12867,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -12288,14 +12875,14 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>109.876</v>
+        <v>25.59377233333336</v>
       </c>
       <c r="G39" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -12312,7 +12899,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12916,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -12337,14 +12924,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>109.876</v>
       </c>
       <c r="G40" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -12378,7 +12965,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -12386,18 +12973,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I41" t="b">
         <v>1</v>
@@ -12407,7 +12995,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12422,7 +13014,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -12430,7 +13022,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -12466,27 +13058,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>23.42490800000007</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>70</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I43" t="b">
         <v>1</v>
@@ -12496,11 +13087,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12515,7 +13102,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -12523,14 +13110,14 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>153.052</v>
+        <v>23.42490800000007</v>
       </c>
       <c r="G44" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -12547,7 +13134,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12564,7 +13151,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -12572,14 +13159,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>153.0518</v>
+        <v>35.09157466666673</v>
       </c>
       <c r="G45" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -12596,7 +13183,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12613,7 +13200,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -12621,170 +13208,170 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G46" t="n">
+        <v>190</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G47" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46">
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48">
         <f>=</f>
         <v/>
       </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D49" t="n">
         <v>2036</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47">
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49">
         <f>=</f>
         <v/>
       </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>27.71964825000006</v>
-      </c>
-      <c r="G48" t="n">
-        <v>70</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2037-06, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>190</v>
-      </c>
-      <c r="G49" t="n">
-        <v>190</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12799,7 +13386,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -12807,14 +13394,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>190</v>
+        <v>27.71964825000006</v>
       </c>
       <c r="G50" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -12831,7 +13418,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12848,7 +13435,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -12856,14 +13443,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>reserved_B_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>17.948</v>
+        <v>43.5529815833334</v>
       </c>
       <c r="G51" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -12880,7 +13467,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2037-06, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12897,7 +13484,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -12905,14 +13492,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>17.9471</v>
+        <v>190</v>
       </c>
       <c r="G52" t="n">
-        <v>17.948</v>
+        <v>190</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -12929,7 +13516,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -12946,7 +13533,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -12954,219 +13541,219 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>190</v>
+      </c>
+      <c r="G53" t="n">
+        <v>190</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>17.948</v>
+      </c>
+      <c r="G54" t="n">
+        <v>110</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>17.9471</v>
+      </c>
+      <c r="G55" t="n">
+        <v>17.948</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53">
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56">
         <f>=</f>
         <v/>
       </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D57" t="n">
         <v>2037</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54">
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57">
         <f>=</f>
         <v/>
       </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>45.37026925000009</v>
-      </c>
-      <c r="G55" t="n">
-        <v>120</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>2038-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>190</v>
-      </c>
-      <c r="G56" t="n">
-        <v>190</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>190</v>
-      </c>
-      <c r="G57" t="n">
-        <v>190</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -13181,7 +13768,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -13189,14 +13776,14 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>reserved_B_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>56.038</v>
+        <v>45.37026925000009</v>
       </c>
       <c r="G58" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -13213,7 +13800,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13230,7 +13817,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -13238,14 +13825,14 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>56.0372</v>
+        <v>69.32860258333342</v>
       </c>
       <c r="G59" t="n">
-        <v>56.038</v>
+        <v>120</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -13262,7 +13849,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2038-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13287,14 +13874,14 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G60" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -13311,7 +13898,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13336,14 +13923,14 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="G61" t="n">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -13360,7 +13947,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13964,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -13385,268 +13972,268 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>56.038</v>
+      </c>
+      <c r="G62" t="n">
+        <v>110</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>56.0372</v>
+      </c>
+      <c r="G63" t="n">
+        <v>56.038</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>120</v>
+      </c>
+      <c r="G64" t="n">
+        <v>120</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>100</v>
+      </c>
+      <c r="G65" t="n">
+        <v>100</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62">
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66">
         <f>=</f>
         <v/>
       </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D67" t="n">
         <v>2038</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63">
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67">
         <f>=</f>
         <v/>
       </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>55.29499044999989</v>
-      </c>
-      <c r="G64" t="n">
-        <v>120</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>2039-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>190</v>
-      </c>
-      <c r="G65" t="n">
-        <v>190</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>190</v>
-      </c>
-      <c r="G66" t="n">
-        <v>190</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>102.515</v>
-      </c>
-      <c r="G67" t="n">
-        <v>110</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -13661,7 +14248,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -13669,14 +14256,14 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>102.5149</v>
+        <v>55.29499044999989</v>
       </c>
       <c r="G68" t="n">
-        <v>102.515</v>
+        <v>120</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -13693,7 +14280,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13710,7 +14297,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -13718,11 +14305,11 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>120</v>
+        <v>85.96165711666657</v>
       </c>
       <c r="G69" t="n">
         <v>120</v>
@@ -13742,7 +14329,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2039-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13759,7 +14346,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -13767,14 +14354,14 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G70" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -13791,7 +14378,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13808,7 +14395,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -13816,317 +14403,317 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>190</v>
+      </c>
+      <c r="G71" t="n">
+        <v>190</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>102.515</v>
+      </c>
+      <c r="G72" t="n">
+        <v>110</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>102.5149</v>
+      </c>
+      <c r="G73" t="n">
+        <v>102.515</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>120</v>
+      </c>
+      <c r="G74" t="n">
+        <v>120</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>120</v>
+      </c>
+      <c r="G75" t="n">
+        <v>120</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71">
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76">
         <f>=</f>
         <v/>
       </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
+      <c r="K76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D77" t="n">
         <v>2039</v>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72">
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77">
         <f>=</f>
         <v/>
       </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>52.49999044999989</v>
-      </c>
-      <c r="G73" t="n">
-        <v>120</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>2040-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>190</v>
-      </c>
-      <c r="G74" t="n">
-        <v>190</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>190</v>
-      </c>
-      <c r="G75" t="n">
-        <v>190</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>110</v>
-      </c>
-      <c r="G76" t="n">
-        <v>110</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>110</v>
-      </c>
-      <c r="G77" t="n">
-        <v>110</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I77" t="b">
-        <v>1</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -14141,7 +14728,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -14149,11 +14736,11 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>120</v>
+        <v>52.49999044999989</v>
       </c>
       <c r="G78" t="n">
         <v>120</v>
@@ -14173,7 +14760,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14190,7 +14777,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -14198,11 +14785,11 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>120</v>
+        <v>89.87499044999988</v>
       </c>
       <c r="G79" t="n">
         <v>120</v>
@@ -14222,7 +14809,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-01, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14239,7 +14826,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -14247,72 +14834,366 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>190</v>
+      </c>
+      <c r="G80" t="n">
+        <v>190</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>190</v>
+      </c>
+      <c r="G81" t="n">
+        <v>190</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>110</v>
+      </c>
+      <c r="G82" t="n">
+        <v>110</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>110</v>
+      </c>
+      <c r="G83" t="n">
+        <v>110</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>120</v>
+      </c>
+      <c r="G84" t="n">
+        <v>120</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>120</v>
+      </c>
+      <c r="G85" t="n">
+        <v>120</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80">
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86">
         <f>=</f>
         <v/>
       </c>
-      <c r="I80" t="b">
-        <v>1</v>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="I86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
+      <c r="K86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D87" t="n">
         <v>2040</v>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81">
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87">
         <f>=</f>
         <v/>
       </c>
-      <c r="I81" t="b">
-        <v>1</v>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="I87" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23651,7 +24532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23693,7 +24574,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13291.585493507</v>
+        <v>13291.955359277</v>
       </c>
     </row>
     <row r="3">
@@ -23713,7 +24594,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10636.65488828602</v>
+        <v>10637.02475405602</v>
       </c>
     </row>
     <row r="4">
@@ -23853,7 +24734,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.664658079209255</v>
+        <v>8.664899191184483</v>
       </c>
     </row>
     <row r="11">
@@ -23873,7 +24754,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.933934086235999</v>
+        <v>6.934175198211227</v>
       </c>
     </row>
     <row r="12">
@@ -24033,7 +24914,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>135.6853910070001</v>
+        <v>136.0552567770001</v>
       </c>
     </row>
     <row r="20">
@@ -24149,11 +25030,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -24169,11 +25050,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -24189,7 +25070,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -24209,11 +25090,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -24229,11 +25110,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -24249,11 +25130,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>80</v>
+      <c r="D32" t="n">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
